--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="192">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -448,6 +448,9 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['25', '34']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -584,6 +587,9 @@
   </si>
   <si>
     <t>['75', '90+1']</t>
+  </si>
+  <si>
+    <t>['9', '59']</t>
   </si>
 </sst>
 </file>
@@ -945,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP91"/>
+  <dimension ref="A1:BP92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1819,7 +1825,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -1897,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2025,7 +2031,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2643,7 +2649,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2849,7 +2855,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -2927,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -3342,7 +3348,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ12">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR12">
         <v>2.03</v>
@@ -3467,7 +3473,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3673,7 +3679,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3879,7 +3885,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4372,7 +4378,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ17">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR17">
         <v>1.8</v>
@@ -4703,7 +4709,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4909,7 +4915,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5115,7 +5121,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5193,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21">
         <v>1.89</v>
@@ -5321,7 +5327,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5402,7 +5408,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR22">
         <v>1.22</v>
@@ -5527,7 +5533,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6145,7 +6151,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6351,7 +6357,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6557,7 +6563,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6763,7 +6769,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7047,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30">
         <v>0.78</v>
@@ -7587,7 +7593,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7793,7 +7799,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -7999,7 +8005,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8286,7 +8292,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ36">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR36">
         <v>1.6</v>
@@ -8901,7 +8907,7 @@
         <v>1.25</v>
       </c>
       <c r="AP39">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>0.89</v>
@@ -9235,7 +9241,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9441,7 +9447,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10059,7 +10065,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10346,7 +10352,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ46">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10471,7 +10477,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10677,7 +10683,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10883,7 +10889,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11089,7 +11095,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11501,7 +11507,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11582,7 +11588,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ52">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR52">
         <v>1.48</v>
@@ -11707,7 +11713,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11913,7 +11919,7 @@
         <v>100</v>
       </c>
       <c r="P54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12119,7 +12125,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12531,7 +12537,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12737,7 +12743,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13021,7 +13027,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ59">
         <v>0</v>
@@ -13149,7 +13155,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13561,7 +13567,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13767,7 +13773,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -13973,7 +13979,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14179,7 +14185,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14385,7 +14391,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14591,7 +14597,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14797,7 +14803,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15209,7 +15215,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15287,7 +15293,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ70">
         <v>1.44</v>
@@ -15621,7 +15627,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15702,7 +15708,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR72">
         <v>1.34</v>
@@ -15827,7 +15833,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16239,7 +16245,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -17269,7 +17275,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17553,7 +17559,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>1.22</v>
@@ -17681,7 +17687,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17887,7 +17893,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18093,7 +18099,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18174,7 +18180,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ84">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR84">
         <v>1.2</v>
@@ -18505,7 +18511,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18711,7 +18717,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18789,7 +18795,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87">
         <v>1</v>
@@ -18917,7 +18923,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19123,7 +19129,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19535,7 +19541,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19692,6 +19698,212 @@
       </c>
       <c r="BP91">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7451056</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45681.58333333334</v>
+      </c>
+      <c r="F92">
+        <v>19</v>
+      </c>
+      <c r="G92" t="s">
+        <v>73</v>
+      </c>
+      <c r="H92" t="s">
+        <v>75</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>3</v>
+      </c>
+      <c r="L92">
+        <v>2</v>
+      </c>
+      <c r="M92">
+        <v>2</v>
+      </c>
+      <c r="N92">
+        <v>4</v>
+      </c>
+      <c r="O92" t="s">
+        <v>144</v>
+      </c>
+      <c r="P92" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q92">
+        <v>1.95</v>
+      </c>
+      <c r="R92">
+        <v>2.3</v>
+      </c>
+      <c r="S92">
+        <v>7.5</v>
+      </c>
+      <c r="T92">
+        <v>1.36</v>
+      </c>
+      <c r="U92">
+        <v>3</v>
+      </c>
+      <c r="V92">
+        <v>2.63</v>
+      </c>
+      <c r="W92">
+        <v>1.44</v>
+      </c>
+      <c r="X92">
+        <v>7</v>
+      </c>
+      <c r="Y92">
+        <v>1.1</v>
+      </c>
+      <c r="Z92">
+        <v>1.4</v>
+      </c>
+      <c r="AA92">
+        <v>4.5</v>
+      </c>
+      <c r="AB92">
+        <v>6.5</v>
+      </c>
+      <c r="AC92">
+        <v>1.04</v>
+      </c>
+      <c r="AD92">
+        <v>9.5</v>
+      </c>
+      <c r="AE92">
+        <v>1.25</v>
+      </c>
+      <c r="AF92">
+        <v>3.75</v>
+      </c>
+      <c r="AG92">
+        <v>1.9</v>
+      </c>
+      <c r="AH92">
+        <v>1.9</v>
+      </c>
+      <c r="AI92">
+        <v>2.2</v>
+      </c>
+      <c r="AJ92">
+        <v>1.62</v>
+      </c>
+      <c r="AK92">
+        <v>1.03</v>
+      </c>
+      <c r="AL92">
+        <v>1.12</v>
+      </c>
+      <c r="AM92">
+        <v>3.1</v>
+      </c>
+      <c r="AN92">
+        <v>1.56</v>
+      </c>
+      <c r="AO92">
+        <v>0.89</v>
+      </c>
+      <c r="AP92">
+        <v>1.5</v>
+      </c>
+      <c r="AQ92">
+        <v>0.9</v>
+      </c>
+      <c r="AR92">
+        <v>1.57</v>
+      </c>
+      <c r="AS92">
+        <v>0.99</v>
+      </c>
+      <c r="AT92">
+        <v>2.56</v>
+      </c>
+      <c r="AU92">
+        <v>4</v>
+      </c>
+      <c r="AV92">
+        <v>6</v>
+      </c>
+      <c r="AW92">
+        <v>5</v>
+      </c>
+      <c r="AX92">
+        <v>9</v>
+      </c>
+      <c r="AY92">
+        <v>9</v>
+      </c>
+      <c r="AZ92">
+        <v>15</v>
+      </c>
+      <c r="BA92">
+        <v>3</v>
+      </c>
+      <c r="BB92">
+        <v>6</v>
+      </c>
+      <c r="BC92">
+        <v>9</v>
+      </c>
+      <c r="BD92">
+        <v>1.32</v>
+      </c>
+      <c r="BE92">
+        <v>8.5</v>
+      </c>
+      <c r="BF92">
+        <v>4.66</v>
+      </c>
+      <c r="BG92">
+        <v>1.32</v>
+      </c>
+      <c r="BH92">
+        <v>3.22</v>
+      </c>
+      <c r="BI92">
+        <v>1.56</v>
+      </c>
+      <c r="BJ92">
+        <v>2.33</v>
+      </c>
+      <c r="BK92">
+        <v>2</v>
+      </c>
+      <c r="BL92">
+        <v>1.8</v>
+      </c>
+      <c r="BM92">
+        <v>2.47</v>
+      </c>
+      <c r="BN92">
+        <v>1.51</v>
+      </c>
+      <c r="BO92">
+        <v>3.35</v>
+      </c>
+      <c r="BP92">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
